--- a/output/2026-09-06_14_Slovenia_Jugovzhodna_Slovenija_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-06_14_Slovenia_Jugovzhodna_Slovenija_Depolverazione_Trattamento_aria.xlsx
@@ -561,7 +561,6 @@
           <t>Impianti meccanici HVAC generici (bassa pertinenza a depolverazione industriale)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Esistenza confermata (mojmojster.net, bizi.si), attiva dal 2008. Telefono/email non verificabili con certezza (dato parziale nella fonte originale) - lasciati vuoti per policy anti-invenzione. ATTENZIONE: non specializzata in depolverazione industriale.</t>
@@ -653,7 +652,6 @@
           <t>ŠILC TRADE d.o.o.</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Jugovzhodna Slovenija - Ribnica</t>
@@ -745,7 +743,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Esistenza confermata (sito ufficiale, metalindustry.info, LinkedIn); ruolo rappresentante Nederman/ULT AG confermato. Telefono/email presi da fonte originale, non riconfermati testualmente in ricerca - verificare puntualmente. Nessuna sede fisica nel sud-est ma copertura nazionale dichiarata.</t>
+          <t>Esistenza confermata (sito ufficiale, metalindustry.info, LinkedIn); ruolo rappresentante Nederman/ULT AG confermato. Telefono/email presi da fonte originale, non riconfermati testualmente in ricerca - verificare puntualmente. Nessuna sede fisica nel sud-est ma copertura nazionale dichiarata. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -819,7 +817,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Esistenza e attivita' confermate (sito ufficiale, bizi.si, mojobrtnik.com): rappresentante Nederman, molto coerente col settore. Telefono/email non riconfermati testualmente - verificare puntualmente. Vedi nota su possibile collegamento con 'industrijsko-odsesovanje.si'.</t>
+          <t>Esistenza e attivita' confermate (sito ufficiale, bizi.si, mojobrtnik.com): rappresentante Nederman, molto coerente col settore. Telefono/email non riconfermati testualmente - verificare puntualmente. Vedi nota su possibile collegamento con 'industrijsko-odsesovanje.si'. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -856,7 +854,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Esistenza confermata (sito ufficiale, bizi.si, itis.siol.net). Prodotto Cartmaster per aspirazione fumi/polveri confermato - coerente col settore. Telefono/email non riconfermati testualmente - verificare puntualmente.</t>
+          <t>Esistenza confermata (sito ufficiale, bizi.si, itis.siol.net). Prodotto Cartmaster per aspirazione fumi/polveri confermato - coerente col settore. Telefono/email non riconfermati testualmente - verificare puntualmente. [DUPLICATO — vedi anche: 2026-09-06_07_Slovenia_Savinjska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -893,7 +891,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Esistenza confermata (sito ufficiale, bizi.si). Attiva dal 1991, prodotti di filtrazione/aspirazione polveri da cabine di sabbiatura confermati. Telefono/email non riconfermati testualmente - verificare puntualmente.</t>
+          <t>Esistenza confermata (sito ufficiale, bizi.si). Attiva dal 1991, prodotti di filtrazione/aspirazione polveri da cabine di sabbiatura confermati. Telefono/email non riconfermati testualmente - verificare puntualmente. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -930,7 +928,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Esistenza confermata (sito ufficiale, mojmojster.net). Rapporto con Bomaksan confermato; Geovent citato su altra pagina non riconfermata in snippet diretto. Telefono/email non riconfermati testualmente - verificare puntualmente. Molto coerente col settore.</t>
+          <t>Esistenza confermata (sito ufficiale, mojmojster.net). Rapporto con Bomaksan confermato; Geovent citato su altra pagina non riconfermata in snippet diretto. Telefono/email non riconfermati testualmente - verificare puntualmente. Molto coerente col settore. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -967,7 +965,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Esistenza confermata (sito ufficiale). Pagina dedicata 'Industrijska filtracija' confermata - coerente col settore. Attiva da oltre 30 anni. Telefono/email non riconfermati testualmente - verificare puntualmente.</t>
+          <t>Esistenza confermata (sito ufficiale). Pagina dedicata 'Industrijska filtracija' confermata - coerente col settore. Attiva da oltre 30 anni. Telefono/email non riconfermati testualmente - verificare puntualmente. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1004,7 +1002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Esistenza confermata (sito ufficiale, LinkedIn). Rivendita aspiratori industriali Delfin confermata - molto coerente col settore. Indirizzo esatto (Britof 27) non riconfermato in snippet, solo citta' Kranj. Telefono/email non riconfermati testualmente - verificare puntualmente.</t>
+          <t>Esistenza confermata (sito ufficiale, LinkedIn). Rivendita aspiratori industriali Delfin confermata - molto coerente col settore. Indirizzo esatto (Britof 27) non riconfermato in snippet, solo citta' Kranj. Telefono/email non riconfermati testualmente - verificare puntualmente. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1041,7 +1039,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Esistenza e telefono confermati (sito ufficiale). Pagina dedicata 'Industrijsko odpraševanje' confermata - molto coerente col settore. Email non riconfermata, lasciata vuota.</t>
+          <t>Esistenza e telefono confermati (sito ufficiale). Pagina dedicata 'Industrijsko odpraševanje' confermata - molto coerente col settore. Email non riconfermata, lasciata vuota. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1115,7 +1113,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Esistenza e telefono confermati (sito ufficiale, bizi.si). Pagine dedicate 'Industrijsko odpraševanje' e 'Prostorska filtracija' confermano piena coerenza col settore. Email non riconfermata, lasciata vuota.</t>
+          <t>Esistenza e telefono confermati (sito ufficiale, bizi.si). Pagine dedicate 'Industrijsko odpraševanje' e 'Prostorska filtracija' confermano piena coerenza col settore. Email non riconfermata, lasciata vuota. [DUPLICATO — vedi anche: 2026-09-05_23_Slovenia_Podravska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1152,7 +1150,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Esistenza confermata (sito ufficiale, bizi.si, ajpes.si). Produttore di filtri a maniche, capacita' 1.000-300.000 m3/h - tra i piu' specializzati della lista. Telefono/email non riconfermati testualmente - verificare puntualmente.</t>
+          <t>Esistenza confermata (sito ufficiale, bizi.si, ajpes.si). Produttore di filtri a maniche, capacita' 1.000-300.000 m3/h - tra i piu' specializzati della lista. Telefono/email non riconfermati testualmente - verificare puntualmente. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1226,7 +1224,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Esistenza e recapiti confermati (itis.siol.net, bizi.si, ebonitete.si, opencorporates.com). Ragione sociale estesa: 'EKOFILTER, podjetje za inženiring, proizvodnjo, prodajo in servis filtracijskih sistemov, d.o.o.'. Molto coerente col settore target.</t>
+          <t>Esistenza e recapiti confermati (itis.siol.net, bizi.si, ebonitete.si, opencorporates.com). Ragione sociale estesa: 'EKOFILTER, podjetje za inženiring, proizvodnjo, prodajo in servis filtracijskih sistemov, d.o.o.'. Molto coerente col settore target. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">

--- a/output/2026-09-06_14_Slovenia_Jugovzhodna_Slovenija_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-06_14_Slovenia_Jugovzhodna_Slovenija_Depolverazione_Trattamento_aria.xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
